--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_daily_max_min_avg_temp.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_daily_max_min_avg_temp.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,37 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,11 +786,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,14 +798,14 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.4</v>
@@ -829,30 +814,30 @@
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="R4" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
+      <c r="S4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,7 +875,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,14 +883,14 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -916,10 +901,10 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -934,8 +919,8 @@
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.2</v>
+      <c r="W5" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -944,7 +929,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,45 +951,45 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="9" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1014,22 +999,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="9" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,37 +1051,37 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>1.9</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
@@ -1104,17 +1089,17 @@
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,30 +1121,30 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1171,17 +1156,17 @@
       <c r="P8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
@@ -1189,10 +1174,10 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
+      <c r="W8" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1215,7 +1200,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1227,10 +1212,10 @@
         <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1223,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="L9" s="9" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="18" t="n">
-        <v>551.2</v>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1239,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="18" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>185.3</v>
+      <c r="R9" s="9" t="n">
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1272,7 +1257,7 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="18" t="n">
+      <c r="W9" s="9" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1298,7 +1283,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
@@ -1318,17 +1303,17 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1337,17 +1322,17 @@
       <c r="P10" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" s="18" t="n">
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="18" t="n">
-        <v>117.7</v>
+      <c r="R10" s="10" t="n">
+        <v>27.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.7</v>
@@ -1355,7 +1340,7 @@
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="18" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1390,26 +1375,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
-        <v>26</v>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,19 +1405,19 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="12" t="n">
-        <v>14.4</v>
+      <c r="S11" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="9" t="n">
@@ -1441,11 +1426,11 @@
       <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1464,7 +1449,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1475,25 +1460,25 @@
       <c r="F12" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>11</v>
+      <c r="K12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,14 +1490,14 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
+      <c r="S12" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>37</v>
@@ -1552,45 +1537,45 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
@@ -1600,18 +1585,18 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>185.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X13" s="12" t="n">
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1637,13 +1622,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>10.5</v>
@@ -1651,19 +1636,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,19 +1658,19 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
@@ -1693,10 +1678,10 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
+      <c r="W14" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X14" s="12" t="n">
+      <c r="X14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1725,13 +1710,13 @@
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1725,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,20 +1745,20 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
@@ -1807,10 +1792,10 @@
       <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="18" t="n">
-        <v>568.1</v>
-      </c>
-      <c r="F16" s="18" t="n">
+      <c r="E16" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1825,26 +1810,26 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M16" s="18" t="n">
+      <c r="L16" s="10" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="18" t="n">
-        <v>1111</v>
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>82.2</v>
@@ -1853,16 +1838,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v>958.2</v>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v>801.9</v>
+        <v>60.9</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,28 +1890,28 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="9" t="n">
@@ -1936,7 +1921,7 @@
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>362</v>
+        <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>18.2</v>
@@ -1944,17 +1929,17 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="18" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>872.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1955,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,30 +1964,30 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="M18" s="17" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>1.6</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
@@ -2014,32 +1999,32 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2067,7 +2052,7 @@
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,10 +2063,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2099,7 +2084,7 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2108,13 +2093,13 @@
       <c r="T19" s="3" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2157,26 +2142,26 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2184,8 +2169,8 @@
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
+      <c r="R20" s="9" t="n">
+        <v>18.1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>15.3</v>
@@ -2193,16 +2178,16 @@
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
@@ -2230,11 +2215,11 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>12.1</v>
@@ -2246,22 +2231,22 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2269,7 +2254,7 @@
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2279,16 +2264,16 @@
         <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
+      <c r="X21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2310,22 +2295,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>12.9</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,20 +2318,20 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2354,14 +2339,14 @@
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>149.5</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2369,17 +2354,17 @@
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
+      <c r="X22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+        <v>13.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,43 +2380,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F23" s="18" t="n">
+        <v>2320.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="18" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="18" t="n">
+      <c r="L23" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="18" t="n">
-        <v>161.8</v>
+      <c r="M23" s="10" t="n">
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.4</v>
@@ -2439,11 +2424,11 @@
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="18" t="n">
-        <v>85</v>
+      <c r="R23" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2454,7 +2439,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="18" t="n">
+      <c r="W23" s="9" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2491,7 +2476,7 @@
       <c r="F24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2501,19 +2486,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L24" s="18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="18" t="n">
+      <c r="M24" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2524,23 +2509,23 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="18" t="n">
+      <c r="R24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="18" t="n">
-        <v>17.7</v>
+      <c r="W24" s="9" t="n">
+        <v>17.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>17.2</v>
@@ -2576,35 +2561,35 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2613,7 +2598,7 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2624,10 +2609,10 @@
       <c r="V25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X25" s="12" t="n">
+      <c r="X25" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2650,7 +2635,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2652,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K26" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2698,28 +2683,28 @@
         <v>16.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
+      <c r="W26" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2723,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,15 +2741,15 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2782,26 +2767,26 @@
       <c r="R27" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="12" t="n">
+      <c r="S27" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="12" t="n">
+      <c r="X27" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2826,16 +2811,16 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,13 +2828,13 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M28" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2879,17 +2864,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="12" t="n">
-        <v>17.8</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2890,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2917,7 +2902,7 @@
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,23 +2913,23 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
@@ -2956,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>27.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2964,14 +2949,14 @@
       <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>11.2</v>
@@ -2990,13 +2975,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>527.1</v>
+        <v>2284.8</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
@@ -3005,7 +2990,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3013,14 +2998,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="18" t="n">
+      <c r="L30" s="9" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="18" t="n">
-        <v>56.7</v>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3031,7 +3016,7 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="18" t="n">
+      <c r="Q30" s="10" t="n">
         <v>413.2</v>
       </c>
       <c r="R30" s="9" t="n">
@@ -3044,12 +3029,12 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3075,7 +3060,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3099,14 +3084,14 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M31" s="18" t="n">
+      <c r="L31" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3117,29 +3102,29 @@
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="18" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="12" t="n">
+      <c r="R31" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+      <c r="U31" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="12" t="n">
+      <c r="X31" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>165.8</v>
@@ -3167,7 +3152,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.7</v>
@@ -3181,16 +3166,16 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="12" t="n">
+      <c r="N32" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3199,31 +3184,31 @@
       <c r="P32" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S32" s="12" t="n">
         <v>18.8</v>
       </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="T32" s="3" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3250,29 +3235,29 @@
       <c r="F33" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G33" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3280,7 +3265,7 @@
       <c r="P33" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
@@ -3293,15 +3278,15 @@
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
+      <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3324,7 +3309,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3338,26 +3323,26 @@
       <c r="G34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>14.7</v>
+      <c r="H34" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3365,7 +3350,7 @@
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
@@ -3378,19 +3363,19 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
+      <c r="X34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3432,10 +3417,10 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="9" t="n">
@@ -3445,18 +3430,18 @@
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="12" t="n">
+      <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3465,7 +3450,7 @@
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="12" t="n">
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
@@ -3475,7 +3460,7 @@
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3500,10 +3485,10 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>15.9</v>
@@ -3512,52 +3497,52 @@
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="12" t="n">
-        <v>19.8</v>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
+      <c r="X36" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>55</v>
@@ -3579,7 +3564,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3591,24 +3576,24 @@
         <v>94.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>63</v>
-      </c>
-      <c r="M37" s="18" t="n">
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3618,32 +3603,32 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="18" t="n">
+      <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="18" t="n">
-        <v>89.90000000000001</v>
+      <c r="R37" s="10" t="n">
+        <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="18" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="18" t="n">
+      <c r="W37" s="10" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3662,7 +3647,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3682,11 +3667,13 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="18" t="n">
+      <c r="J38" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M38" s="9" t="n">
@@ -3696,37 +3683,37 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>298.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="12" t="n">
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="12" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="V38" s="18" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
+      <c r="X38" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3748,7 +3735,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3756,54 +3743,54 @@
       <c r="F39" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
       </c>
       <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
-        <v>14.9</v>
+      <c r="N39" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>14.6</v>
@@ -3812,7 +3799,7 @@
         <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3828,7 +3815,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3851,46 +3838,46 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="12" t="n">
+      <c r="S40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>169.5</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
+      <c r="X40" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y40" s="3" t="n">
@@ -3916,51 +3903,51 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
+        <v>28.4</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3969,11 +3956,11 @@
       <c r="U41" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>16.3</v>
@@ -3982,7 +3969,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4004,31 +3991,31 @@
         <v>27.2</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>1.1</v>
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>125.7</v>
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -4042,22 +4029,22 @@
       <c r="Q42" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4078,25 +4065,25 @@
         <v>0.1</v>
       </c>
       <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
       <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4117,25 +4104,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4153,51 +4140,51 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
-      </c>
-      <c r="D45" s="18" t="n">
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="18" t="n">
-        <v>41.8</v>
+      <c r="E45" s="9" t="n">
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>107.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="18" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="18" t="n">
+      <c r="M45" s="9" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q45" s="18" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="18" t="n">
+      <c r="R45" s="9" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4209,14 +4196,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="18" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="18" t="n">
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="10" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4259,13 +4246,13 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>111.7</v>
+        <v>52.1</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>11.8</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>10.7</v>
@@ -4274,18 +4261,18 @@
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4294,20 +4281,20 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="18" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>265.7</v>
+        <v>65.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
